--- a/exports/trend_1d/BRITANNIA_full_report.xlsx
+++ b/exports/trend_1d/BRITANNIA_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q71"/>
+  <dimension ref="A1:U71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>7.98</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42114</v>
+        <v>42115</v>
       </c>
       <c r="H2" t="n">
-        <v>1085</v>
+        <v>1034.75</v>
       </c>
       <c r="I2" t="n">
         <v>1073.703624064102</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K2" t="n">
-        <v>12.19</v>
+        <v>7</v>
       </c>
       <c r="L2" t="n">
         <v>4.54</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>14.29</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42128</v>
+        <v>42129</v>
       </c>
       <c r="H3" t="n">
-        <v>1124.2</v>
+        <v>1172.47</v>
       </c>
       <c r="I3" t="n">
         <v>1166.284401926389</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K3" t="n">
-        <v>-8.640000000000001</v>
+        <v>-13.31</v>
       </c>
       <c r="L3" t="n">
-        <v>9.210000000000001</v>
+        <v>14.73</v>
       </c>
       <c r="M3" t="n">
         <v>0.85</v>
       </c>
       <c r="N3" t="n">
-        <v>4.13</v>
+        <v>4.29</v>
       </c>
       <c r="O3" t="n">
         <v>-4.63</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>12.55</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42237</v>
+        <v>42240</v>
       </c>
       <c r="H4" t="n">
-        <v>1599.67</v>
+        <v>1501.12</v>
       </c>
       <c r="I4" t="n">
         <v>1555.609564596554</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="K4" t="n">
-        <v>36.44</v>
+        <v>28.03</v>
       </c>
       <c r="L4" t="n">
         <v>6.58</v>
@@ -669,7 +716,7 @@
         <v>1.79</v>
       </c>
       <c r="N4" t="n">
-        <v>4.24</v>
+        <v>6.16</v>
       </c>
       <c r="O4" t="n">
         <v>4.29</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>4</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>11.7</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42278</v>
+        <v>42282</v>
       </c>
       <c r="H5" t="n">
-        <v>1561.4</v>
+        <v>1606.82</v>
       </c>
       <c r="I5" t="n">
         <v>1588.295314844406</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K5" t="n">
-        <v>-4.02</v>
+        <v>-7.04</v>
       </c>
       <c r="L5" t="n">
-        <v>4.91</v>
+        <v>7.55</v>
       </c>
       <c r="M5" t="n">
         <v>1.99</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>10.12</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42314</v>
+        <v>42317</v>
       </c>
       <c r="H6" t="n">
-        <v>1565</v>
+        <v>1522.27</v>
       </c>
       <c r="I6" t="n">
         <v>1528.051638383609</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.6</v>
+        <v>-5.26</v>
       </c>
       <c r="L6" t="n">
-        <v>4.05</v>
+        <v>5.56</v>
       </c>
       <c r="M6" t="n">
-        <v>1.23</v>
+        <v>1.76</v>
       </c>
       <c r="N6" t="n">
-        <v>1.75</v>
+        <v>2.73</v>
       </c>
       <c r="O6" t="n">
         <v>2.91</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>9.32</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42404</v>
+        <v>42405</v>
       </c>
       <c r="H7" t="n">
-        <v>1428.15</v>
+        <v>1431.25</v>
       </c>
       <c r="I7" t="n">
         <v>1428.834790281344</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K7" t="n">
-        <v>6.18</v>
+        <v>5.98</v>
       </c>
       <c r="L7" t="n">
         <v>3.3</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>8.949999999999999</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42410</v>
+        <v>42411</v>
       </c>
       <c r="H8" t="n">
-        <v>1361</v>
+        <v>1317</v>
       </c>
       <c r="I8" t="n">
         <v>1326.113730915554</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K8" t="n">
-        <v>-4.91</v>
+        <v>-7.98</v>
       </c>
       <c r="L8" t="n">
-        <v>6.11</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>0.45</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>2.51</v>
+        <v>3.23</v>
       </c>
       <c r="O8" t="n">
         <v>0.22</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42425</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>12.62</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42473</v>
+        <v>42478</v>
       </c>
       <c r="H9" t="n">
-        <v>1380.55</v>
+        <v>1425.32</v>
       </c>
       <c r="I9" t="n">
         <v>1406.696814381194</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="K9" t="n">
-        <v>-4.83</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="L9" t="n">
         <v>10.65</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42425</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,28 +1109,28 @@
         <v>8.93</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42510</v>
+        <v>42513</v>
       </c>
       <c r="H10" t="n">
-        <v>1465.35</v>
+        <v>1341.25</v>
       </c>
       <c r="I10" t="n">
         <v>1407.446960912659</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K10" t="n">
-        <v>2.81</v>
+        <v>-5.9</v>
       </c>
       <c r="L10" t="n">
-        <v>2.81</v>
+        <v>6.65</v>
       </c>
       <c r="M10" t="n">
-        <v>0.39</v>
+        <v>2.75</v>
       </c>
       <c r="N10" t="n">
-        <v>2.18</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="O10" t="n">
         <v>3.24</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42488</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>12.45</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42549</v>
+        <v>42550</v>
       </c>
       <c r="H11" t="n">
-        <v>1374.07</v>
+        <v>1385.7</v>
       </c>
       <c r="I11" t="n">
         <v>1375.280025535347</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.45</v>
+        <v>-3.31</v>
       </c>
       <c r="L11" t="n">
         <v>6.24</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>7.95</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42641</v>
+        <v>42642</v>
       </c>
       <c r="H12" t="n">
-        <v>1702.1</v>
+        <v>1642.77</v>
       </c>
       <c r="I12" t="n">
         <v>1653.939166731928</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K12" t="n">
-        <v>22.83</v>
+        <v>18.55</v>
       </c>
       <c r="L12" t="n">
         <v>2.33</v>
@@ -1125,7 +1268,7 @@
         <v>1.59</v>
       </c>
       <c r="N12" t="n">
-        <v>2</v>
+        <v>3.49</v>
       </c>
       <c r="O12" t="n">
         <v>0.85</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>4</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>9.140000000000001</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42751</v>
+        <v>42752</v>
       </c>
       <c r="H13" t="n">
-        <v>1482.87</v>
+        <v>1506.77</v>
       </c>
       <c r="I13" t="n">
         <v>1497.314027174968</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K13" t="n">
-        <v>9.73</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="L13" t="n">
         <v>7.2</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>4</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>6.82</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42800</v>
+        <v>42801</v>
       </c>
       <c r="H14" t="n">
-        <v>1543</v>
+        <v>1529.57</v>
       </c>
       <c r="I14" t="n">
         <v>1535.174667755213</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K14" t="n">
-        <v>2.4</v>
+        <v>1.51</v>
       </c>
       <c r="L14" t="n">
         <v>1.94</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>6.98</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42814</v>
+        <v>42815</v>
       </c>
       <c r="H15" t="n">
-        <v>1625.87</v>
+        <v>1647.17</v>
       </c>
       <c r="I15" t="n">
         <v>1632.664525096727</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K15" t="n">
-        <v>-6.3</v>
+        <v>-7.69</v>
       </c>
       <c r="L15" t="n">
-        <v>6.71</v>
+        <v>8.56</v>
       </c>
       <c r="M15" t="n">
         <v>1</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42824</v>
+      </c>
+      <c r="S15" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>5.65</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42880</v>
+        <v>42881</v>
       </c>
       <c r="H16" t="n">
-        <v>1758.9</v>
+        <v>1707.92</v>
       </c>
       <c r="I16" t="n">
         <v>1743.84916115088</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K16" t="n">
-        <v>6.78</v>
+        <v>3.69</v>
       </c>
       <c r="L16" t="n">
         <v>1.65</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42824</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>4</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>11.06</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42919</v>
+        <v>42920</v>
       </c>
       <c r="H17" t="n">
-        <v>1851.87</v>
+        <v>1874.02</v>
       </c>
       <c r="I17" t="n">
         <v>1859.340157343988</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K17" t="n">
-        <v>-8.43</v>
+        <v>-9.73</v>
       </c>
       <c r="L17" t="n">
-        <v>9.68</v>
+        <v>10.31</v>
       </c>
       <c r="M17" t="n">
         <v>1.48</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42915</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,25 +1661,25 @@
         <v>6.43</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43136</v>
+        <v>43137</v>
       </c>
       <c r="H18" t="n">
-        <v>2308.35</v>
+        <v>2265.22</v>
       </c>
       <c r="I18" t="n">
         <v>2291.519252990347</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K18" t="n">
-        <v>23.18</v>
+        <v>20.87</v>
       </c>
       <c r="L18" t="n">
         <v>2.45</v>
       </c>
       <c r="M18" t="n">
-        <v>2.01</v>
+        <v>2.53</v>
       </c>
       <c r="N18" t="n">
         <v>2.49</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>148</v>
+        <v>149</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>8</v>
+      </c>
+      <c r="U18" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>7.55</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43153</v>
+        <v>43154</v>
       </c>
       <c r="H19" t="n">
-        <v>2427.92</v>
+        <v>2480.95</v>
       </c>
       <c r="I19" t="n">
         <v>2436.318232363663</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K19" t="n">
-        <v>-7.18</v>
+        <v>-9.52</v>
       </c>
       <c r="L19" t="n">
-        <v>7.62</v>
+        <v>9.9</v>
       </c>
       <c r="M19" t="n">
         <v>1.94</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>7.32</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43318</v>
+        <v>43319</v>
       </c>
       <c r="H20" t="n">
-        <v>3163.35</v>
+        <v>3100.2</v>
       </c>
       <c r="I20" t="n">
         <v>3118.388167832161</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="K20" t="n">
-        <v>27.51</v>
+        <v>24.96</v>
       </c>
       <c r="L20" t="n">
         <v>3.67</v>
@@ -1581,7 +1820,7 @@
         <v>0.89</v>
       </c>
       <c r="N20" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="O20" t="n">
         <v>2.18</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>113</v>
+        <v>114</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43187</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>6</v>
+      </c>
+      <c r="U20" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>8.49</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43329</v>
+        <v>43332</v>
       </c>
       <c r="H21" t="n">
-        <v>3314.95</v>
+        <v>3385.7</v>
       </c>
       <c r="I21" t="n">
         <v>3357.143523177383</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K21" t="n">
-        <v>-6.93</v>
+        <v>-9.210000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>7.1</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>0.5</v>
+        <v>0.59</v>
       </c>
       <c r="N21" t="n">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="O21" t="n">
         <v>-2</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>6.65</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43346</v>
+        <v>43347</v>
       </c>
       <c r="H22" t="n">
-        <v>3282.92</v>
+        <v>3172.02</v>
       </c>
       <c r="I22" t="n">
         <v>3237.778306288075</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K22" t="n">
-        <v>-3.04</v>
+        <v>-6.31</v>
       </c>
       <c r="L22" t="n">
-        <v>3.54</v>
+        <v>6.97</v>
       </c>
       <c r="M22" t="n">
-        <v>0.15</v>
+        <v>0.45</v>
       </c>
       <c r="N22" t="n">
-        <v>2.54</v>
+        <v>3.38</v>
       </c>
       <c r="O22" t="n">
         <v>2.13</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>9.449999999999999</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43419</v>
+        <v>43420</v>
       </c>
       <c r="H23" t="n">
-        <v>2909.07</v>
+        <v>2973.82</v>
       </c>
       <c r="I23" t="n">
         <v>2943.736176873997</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K23" t="n">
-        <v>8.289999999999999</v>
+        <v>6.25</v>
       </c>
       <c r="L23" t="n">
         <v>4.17</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>9.470000000000001</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43507</v>
+        <v>43508</v>
       </c>
       <c r="H24" t="n">
-        <v>3107.55</v>
+        <v>3008.6</v>
       </c>
       <c r="I24" t="n">
         <v>3073.361575467869</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K24" t="n">
-        <v>4.5</v>
+        <v>1.17</v>
       </c>
       <c r="L24" t="n">
         <v>2.65</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>4</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>9.42</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43532</v>
+        <v>43535</v>
       </c>
       <c r="H25" t="n">
-        <v>3071.2</v>
+        <v>3133.45</v>
       </c>
       <c r="I25" t="n">
         <v>3125.835488269245</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.08</v>
+        <v>-4.15</v>
       </c>
       <c r="L25" t="n">
-        <v>3.34</v>
+        <v>4.35</v>
       </c>
       <c r="M25" t="n">
         <v>0.85</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>7.92</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43581</v>
+        <v>43585</v>
       </c>
       <c r="H26" t="n">
-        <v>2967.7</v>
+        <v>2896.05</v>
       </c>
       <c r="I26" t="n">
         <v>2938.821767743233</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="K26" t="n">
-        <v>-5.29</v>
+        <v>-7.58</v>
       </c>
       <c r="L26" t="n">
-        <v>6.17</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="M26" t="n">
         <v>0.77</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>6.32</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43605</v>
+        <v>43606</v>
       </c>
       <c r="H27" t="n">
-        <v>2801.2</v>
+        <v>2848.7</v>
       </c>
       <c r="I27" t="n">
         <v>2840.819990346176</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K27" t="n">
-        <v>3.28</v>
+        <v>1.63</v>
       </c>
       <c r="L27" t="n">
         <v>2.72</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>7.26</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43637</v>
+        <v>43640</v>
       </c>
       <c r="H28" t="n">
-        <v>2826.7</v>
+        <v>2780.5</v>
       </c>
       <c r="I28" t="n">
         <v>2795.212793594755</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.77</v>
+        <v>-2.39</v>
       </c>
       <c r="L28" t="n">
-        <v>1.92</v>
+        <v>2.73</v>
       </c>
       <c r="M28" t="n">
         <v>0.89</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>8.380000000000001</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43703</v>
+        <v>43704</v>
       </c>
       <c r="H29" t="n">
-        <v>2533.85</v>
+        <v>2685.9</v>
       </c>
       <c r="I29" t="n">
         <v>2580.167279861593</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K29" t="n">
-        <v>8.869999999999999</v>
+        <v>3.4</v>
       </c>
       <c r="L29" t="n">
         <v>3.04</v>
@@ -2094,7 +2441,7 @@
         <v>1.5</v>
       </c>
       <c r="N29" t="n">
-        <v>2.72</v>
+        <v>6</v>
       </c>
       <c r="O29" t="n">
         <v>-1.63</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43643</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>12.39</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43790</v>
+        <v>43791</v>
       </c>
       <c r="H30" t="n">
-        <v>3072.65</v>
+        <v>3022.65</v>
       </c>
       <c r="I30" t="n">
         <v>3071.039645069205</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K30" t="n">
-        <v>14.4</v>
+        <v>12.54</v>
       </c>
       <c r="L30" t="n">
         <v>5.8</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>4</v>
+      </c>
+      <c r="U30" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>8.48</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43845</v>
+        <v>43846</v>
       </c>
       <c r="H31" t="n">
-        <v>3114.2</v>
+        <v>3150.25</v>
       </c>
       <c r="I31" t="n">
         <v>3127.895872865392</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K31" t="n">
-        <v>-3.03</v>
+        <v>-4.22</v>
       </c>
       <c r="L31" t="n">
-        <v>4.41</v>
+        <v>4.54</v>
       </c>
       <c r="M31" t="n">
         <v>0.78</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,22 +2627,22 @@
         <v>5.04</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43881</v>
+        <v>43885</v>
       </c>
       <c r="H32" t="n">
-        <v>3059.4</v>
+        <v>3036.2</v>
       </c>
       <c r="I32" t="n">
         <v>3053.918094956362</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="K32" t="n">
-        <v>-2.88</v>
+        <v>-3.62</v>
       </c>
       <c r="L32" t="n">
-        <v>4.13</v>
+        <v>4.61</v>
       </c>
       <c r="M32" t="n">
         <v>1.24</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>7.01</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43941</v>
+        <v>43942</v>
       </c>
       <c r="H33" t="n">
-        <v>2833</v>
+        <v>2863.25</v>
       </c>
       <c r="I33" t="n">
         <v>2857.308703071407</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K33" t="n">
-        <v>6.69</v>
+        <v>5.7</v>
       </c>
       <c r="L33" t="n">
         <v>4.24</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>19.02</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44077</v>
+        <v>44078</v>
       </c>
       <c r="H34" t="n">
-        <v>3746.85</v>
+        <v>3705.85</v>
       </c>
       <c r="I34" t="n">
         <v>3709.77131144332</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="K34" t="n">
-        <v>30.86</v>
+        <v>29.43</v>
       </c>
       <c r="L34" t="n">
         <v>4.54</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>96</v>
+        <v>97</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>6</v>
+      </c>
+      <c r="U34" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>7.52</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44174</v>
+        <v>44175</v>
       </c>
       <c r="H35" t="n">
-        <v>3627.1</v>
+        <v>3739.75</v>
       </c>
       <c r="I35" t="n">
         <v>3688.199788507707</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K35" t="n">
-        <v>2.13</v>
+        <v>-0.91</v>
       </c>
       <c r="L35" t="n">
         <v>4.99</v>
@@ -2436,7 +2855,7 @@
         <v>1.77</v>
       </c>
       <c r="N35" t="n">
-        <v>2.96</v>
+        <v>3.11</v>
       </c>
       <c r="O35" t="n">
         <v>-1.09</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>4</v>
+      </c>
+      <c r="U35" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>7.43</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44197</v>
+        <v>44200</v>
       </c>
       <c r="H36" t="n">
-        <v>3567.8</v>
+        <v>3552.9</v>
       </c>
       <c r="I36" t="n">
         <v>3556.064533849689</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K36" t="n">
-        <v>-4.6</v>
+        <v>-5</v>
       </c>
       <c r="L36" t="n">
         <v>5.48</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44196</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>5.93</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44274</v>
+        <v>44277</v>
       </c>
       <c r="H37" t="n">
-        <v>3466.6</v>
+        <v>3564.4</v>
       </c>
       <c r="I37" t="n">
         <v>3536.186864235097</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="K37" t="n">
-        <v>2.43</v>
+        <v>-0.32</v>
       </c>
       <c r="L37" t="n">
         <v>4.28</v>
@@ -2550,7 +2993,7 @@
         <v>1.68</v>
       </c>
       <c r="N37" t="n">
-        <v>2.09</v>
+        <v>2.82</v>
       </c>
       <c r="O37" t="n">
         <v>-0.42</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>7.77</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44309</v>
+        <v>44312</v>
       </c>
       <c r="H38" t="n">
-        <v>3650.3</v>
+        <v>3539.2</v>
       </c>
       <c r="I38" t="n">
         <v>3588.273004354335</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K38" t="n">
-        <v>2.41</v>
+        <v>-0.71</v>
       </c>
       <c r="L38" t="n">
         <v>3.8</v>
@@ -2607,7 +3062,7 @@
         <v>0.91</v>
       </c>
       <c r="N38" t="n">
-        <v>2.71</v>
+        <v>3.04</v>
       </c>
       <c r="O38" t="n">
         <v>2.82</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>9.31</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44354</v>
+        <v>44355</v>
       </c>
       <c r="H39" t="n">
-        <v>3542.6</v>
+        <v>3601.75</v>
       </c>
       <c r="I39" t="n">
         <v>3594.661127444534</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.1</v>
+        <v>-1.77</v>
       </c>
       <c r="L39" t="n">
         <v>3.47</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,25 +3179,25 @@
         <v>4.95</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44384</v>
+        <v>44385</v>
       </c>
       <c r="H40" t="n">
-        <v>3521.35</v>
+        <v>3491.4</v>
       </c>
       <c r="I40" t="n">
         <v>3508.104237718643</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K40" t="n">
-        <v>-2.23</v>
+        <v>-3.06</v>
       </c>
       <c r="L40" t="n">
-        <v>2.66</v>
+        <v>3.57</v>
       </c>
       <c r="M40" t="n">
-        <v>0.53</v>
+        <v>0.63</v>
       </c>
       <c r="N40" t="n">
         <v>1.48</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44371</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,25 +3248,25 @@
         <v>4.98</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44410</v>
+        <v>44411</v>
       </c>
       <c r="H41" t="n">
-        <v>3504.65</v>
+        <v>3573.2</v>
       </c>
       <c r="I41" t="n">
         <v>3552.478186819831</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.38</v>
+        <v>-2.34</v>
       </c>
       <c r="L41" t="n">
-        <v>1.45</v>
+        <v>2.51</v>
       </c>
       <c r="M41" t="n">
-        <v>0.68</v>
+        <v>1.29</v>
       </c>
       <c r="N41" t="n">
         <v>2.37</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>5.28</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44470</v>
+        <v>44473</v>
       </c>
       <c r="H42" t="n">
-        <v>3921.1</v>
+        <v>3892.9</v>
       </c>
       <c r="I42" t="n">
         <v>3892.963652457254</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K42" t="n">
-        <v>9.74</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="L42" t="n">
         <v>1.18</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>6.31</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44567</v>
+        <v>44568</v>
       </c>
       <c r="H43" t="n">
-        <v>3675.1</v>
+        <v>3737.35</v>
       </c>
       <c r="I43" t="n">
         <v>3693.892701478636</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K43" t="n">
-        <v>5.59</v>
+        <v>4</v>
       </c>
       <c r="L43" t="n">
         <v>2.58</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>4</v>
+      </c>
+      <c r="U43" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>5.3</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44579</v>
+        <v>44580</v>
       </c>
       <c r="H44" t="n">
-        <v>3621.9</v>
+        <v>3575.65</v>
       </c>
       <c r="I44" t="n">
         <v>3596.944288579204</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K44" t="n">
-        <v>-3.09</v>
+        <v>-4.33</v>
       </c>
       <c r="L44" t="n">
-        <v>3.38</v>
+        <v>4.61</v>
       </c>
       <c r="M44" t="n">
         <v>0.41</v>
       </c>
       <c r="N44" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="O44" t="n">
         <v>1.69</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>5.86</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44658</v>
+        <v>44659</v>
       </c>
       <c r="H45" t="n">
-        <v>3294.1</v>
+        <v>3347.9</v>
       </c>
       <c r="I45" t="n">
         <v>3339.946971567928</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K45" t="n">
-        <v>7.87</v>
+        <v>6.37</v>
       </c>
       <c r="L45" t="n">
         <v>3.76</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>4</v>
+      </c>
+      <c r="U45" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>6.77</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44728</v>
+        <v>44729</v>
       </c>
       <c r="H46" t="n">
-        <v>3390.4</v>
+        <v>3332.1</v>
       </c>
       <c r="I46" t="n">
         <v>3339.658325963343</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K46" t="n">
-        <v>1.27</v>
+        <v>-0.47</v>
       </c>
       <c r="L46" t="n">
         <v>6.45</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>7.92</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44743</v>
+        <v>44746</v>
       </c>
       <c r="H47" t="n">
-        <v>3584.35</v>
+        <v>3700.45</v>
       </c>
       <c r="I47" t="n">
         <v>3595.995435864052</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K47" t="n">
-        <v>-7.57</v>
+        <v>-11.05</v>
       </c>
       <c r="L47" t="n">
-        <v>8.039999999999999</v>
+        <v>11.44</v>
       </c>
       <c r="M47" t="n">
         <v>0.9399999999999999</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>9.630000000000001</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44778</v>
+        <v>44781</v>
       </c>
       <c r="H48" t="n">
-        <v>3688.1</v>
+        <v>3631.4</v>
       </c>
       <c r="I48" t="n">
         <v>3675.783144902066</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.33</v>
+        <v>-1.87</v>
       </c>
       <c r="L48" t="n">
         <v>3.39</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>8.140000000000001</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44831</v>
+        <v>44832</v>
       </c>
       <c r="H49" t="n">
-        <v>3824.15</v>
+        <v>3853.2</v>
       </c>
       <c r="I49" t="n">
         <v>3831.064692177488</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K49" t="n">
-        <v>-5.31</v>
+        <v>-6.11</v>
       </c>
       <c r="L49" t="n">
         <v>7.12</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>6.77</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44925</v>
+        <v>44928</v>
       </c>
       <c r="H50" t="n">
-        <v>4307.45</v>
+        <v>4292.15</v>
       </c>
       <c r="I50" t="n">
         <v>4294.638689404221</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="K50" t="n">
-        <v>11.79</v>
+        <v>11.39</v>
       </c>
       <c r="L50" t="n">
         <v>4.24</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>5</v>
+      </c>
+      <c r="U50" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>6.12</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44958</v>
+        <v>44959</v>
       </c>
       <c r="H51" t="n">
-        <v>4370.95</v>
+        <v>4573.05</v>
       </c>
       <c r="I51" t="n">
         <v>4472.386673583041</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K51" t="n">
-        <v>-1.84</v>
+        <v>-6.54</v>
       </c>
       <c r="L51" t="n">
-        <v>3.55</v>
+        <v>7.08</v>
       </c>
       <c r="M51" t="n">
-        <v>1.68</v>
+        <v>3.39</v>
       </c>
       <c r="N51" t="n">
-        <v>1.85</v>
+        <v>4.62</v>
       </c>
       <c r="O51" t="n">
         <v>-0.36</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>8.5</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>44988</v>
+        <v>44991</v>
       </c>
       <c r="H52" t="n">
-        <v>4411.95</v>
+        <v>4319.85</v>
       </c>
       <c r="I52" t="n">
         <v>4378.322988773788</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K52" t="n">
-        <v>-3.52</v>
+        <v>-5.54</v>
       </c>
       <c r="L52" t="n">
-        <v>5.03</v>
+        <v>6.41</v>
       </c>
       <c r="M52" t="n">
         <v>0.52</v>
       </c>
       <c r="N52" t="n">
-        <v>1.84</v>
+        <v>2.09</v>
       </c>
       <c r="O52" t="n">
         <v>4.62</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>6.15</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45042</v>
+        <v>45043</v>
       </c>
       <c r="H53" t="n">
-        <v>4405</v>
+        <v>4415.85</v>
       </c>
       <c r="I53" t="n">
         <v>4410.97416072935</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K53" t="n">
-        <v>-1.97</v>
+        <v>-2.22</v>
       </c>
       <c r="L53" t="n">
-        <v>2.38</v>
+        <v>2.53</v>
       </c>
       <c r="M53" t="n">
         <v>0.57</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>4.78</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45131</v>
+        <v>45132</v>
       </c>
       <c r="H54" t="n">
-        <v>4968.9</v>
+        <v>4885.6</v>
       </c>
       <c r="I54" t="n">
         <v>4929.262612270457</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K54" t="n">
-        <v>12.52</v>
+        <v>10.64</v>
       </c>
       <c r="L54" t="n">
         <v>0.43</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>7.12</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45233</v>
+        <v>45236</v>
       </c>
       <c r="H55" t="n">
-        <v>4539.55</v>
+        <v>4623.6</v>
       </c>
       <c r="I55" t="n">
         <v>4608.845228940582</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="K55" t="n">
-        <v>7.08</v>
+        <v>5.36</v>
       </c>
       <c r="L55" t="n">
         <v>2.67</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>5</v>
+      </c>
+      <c r="U55" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>5.87</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45329</v>
+        <v>45330</v>
       </c>
       <c r="H56" t="n">
-        <v>5078.25</v>
+        <v>4875.55</v>
       </c>
       <c r="I56" t="n">
         <v>5004.30479360846</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K56" t="n">
-        <v>9.83</v>
+        <v>5.45</v>
       </c>
       <c r="L56" t="n">
         <v>1.68</v>
@@ -3633,7 +4304,7 @@
         <v>0.57</v>
       </c>
       <c r="N56" t="n">
-        <v>2.29</v>
+        <v>3.99</v>
       </c>
       <c r="O56" t="n">
         <v>1.85</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>4</v>
+      </c>
+      <c r="U56" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>11.6</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45415</v>
+        <v>45418</v>
       </c>
       <c r="H57" t="n">
-        <v>4744.6</v>
+        <v>5061.6</v>
       </c>
       <c r="I57" t="n">
         <v>4918.306204581213</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="K57" t="n">
-        <v>2.69</v>
+        <v>-3.82</v>
       </c>
       <c r="L57" t="n">
-        <v>5.06</v>
+        <v>6.77</v>
       </c>
       <c r="M57" t="n">
-        <v>0.5</v>
+        <v>1.57</v>
       </c>
       <c r="N57" t="n">
-        <v>1.98</v>
+        <v>6.68</v>
       </c>
       <c r="O57" t="n">
         <v>-3.99</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>4</v>
+      </c>
+      <c r="U57" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>7.94</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45574</v>
+        <v>45575</v>
       </c>
       <c r="H58" t="n">
-        <v>6097.25</v>
+        <v>6002.15</v>
       </c>
       <c r="I58" t="n">
         <v>6041.223016222864</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K58" t="n">
-        <v>20.46</v>
+        <v>18.58</v>
       </c>
       <c r="L58" t="n">
         <v>5.12</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>109</v>
+        <v>110</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>6</v>
+      </c>
+      <c r="U58" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>7.95</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45679</v>
+        <v>45680</v>
       </c>
       <c r="H59" t="n">
-        <v>4956.7</v>
+        <v>5012.6</v>
       </c>
       <c r="I59" t="n">
         <v>4987.117896234087</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K59" t="n">
-        <v>17.42</v>
+        <v>16.49</v>
       </c>
       <c r="L59" t="n">
         <v>2.63</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>4</v>
+      </c>
+      <c r="U59" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="60">
@@ -3840,22 +4559,22 @@
         <v>7.41</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45706</v>
+        <v>45707</v>
       </c>
       <c r="H60" t="n">
-        <v>4891.2</v>
+        <v>4837.5</v>
       </c>
       <c r="I60" t="n">
         <v>4838.325889789324</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K60" t="n">
-        <v>-2.42</v>
+        <v>-3.49</v>
       </c>
       <c r="L60" t="n">
-        <v>3.37</v>
+        <v>3.99</v>
       </c>
       <c r="M60" t="n">
         <v>0.25</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>7.36</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45743</v>
+        <v>45744</v>
       </c>
       <c r="H61" t="n">
-        <v>4841.2</v>
+        <v>4936.9</v>
       </c>
       <c r="I61" t="n">
         <v>4886.563957377023</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K61" t="n">
-        <v>-0.08</v>
+        <v>-2.05</v>
       </c>
       <c r="L61" t="n">
-        <v>1.82</v>
+        <v>3.95</v>
       </c>
       <c r="M61" t="n">
         <v>0.74</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>3</v>
+      </c>
+      <c r="U61" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>7.06</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45874</v>
+        <v>45875</v>
       </c>
       <c r="H62" t="n">
-        <v>5635.5</v>
+        <v>5402.5</v>
       </c>
       <c r="I62" t="n">
         <v>5572.293915139694</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K62" t="n">
-        <v>14.15</v>
+        <v>9.43</v>
       </c>
       <c r="L62" t="n">
         <v>6.72</v>
@@ -3975,7 +4718,7 @@
         <v>7.99</v>
       </c>
       <c r="N62" t="n">
-        <v>2.62</v>
+        <v>4.13</v>
       </c>
       <c r="O62" t="n">
         <v>1.98</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>5</v>
+      </c>
+      <c r="U62" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="63">
@@ -4011,28 +4766,28 @@
         <v>8.789999999999999</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45888</v>
+        <v>45889</v>
       </c>
       <c r="H63" t="n">
-        <v>5499</v>
+        <v>5701</v>
       </c>
       <c r="I63" t="n">
         <v>5698.6075777367</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K63" t="n">
-        <v>-1.79</v>
+        <v>-5.53</v>
       </c>
       <c r="L63" t="n">
-        <v>4.9</v>
+        <v>6.15</v>
       </c>
       <c r="M63" t="n">
         <v>1.84</v>
       </c>
       <c r="N63" t="n">
-        <v>2.57</v>
+        <v>3.67</v>
       </c>
       <c r="O63" t="n">
         <v>-4.13</v>
@@ -4041,7 +4796,19 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>9.619999999999999</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="H64" t="n">
-        <v>5887</v>
+        <v>5836</v>
       </c>
       <c r="I64" t="n">
         <v>5838.458915046706</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K64" t="n">
-        <v>3.26</v>
+        <v>2.37</v>
       </c>
       <c r="L64" t="n">
         <v>3.96</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>3</v>
+      </c>
+      <c r="U64" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>6.11</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="H65" t="n">
-        <v>6013.5</v>
+        <v>6157.5</v>
       </c>
       <c r="I65" t="n">
         <v>6144.7416152963</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K65" t="n">
-        <v>-3.04</v>
+        <v>-5.51</v>
       </c>
       <c r="L65" t="n">
         <v>6.09</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>8.77</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46041</v>
+        <v>46042</v>
       </c>
       <c r="H66" t="n">
-        <v>5943.5</v>
+        <v>5884</v>
       </c>
       <c r="I66" t="n">
         <v>5888.308454479818</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K66" t="n">
-        <v>-3.48</v>
+        <v>-4.44</v>
       </c>
       <c r="L66" t="n">
         <v>7.06</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>3</v>
+      </c>
+      <c r="U66" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>6.45</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="H67" t="n">
-        <v>6019</v>
+        <v>6102</v>
       </c>
       <c r="I67" t="n">
         <v>6089.691549629805</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K67" t="n">
-        <v>-2.29</v>
+        <v>-3.7</v>
       </c>
       <c r="L67" t="n">
         <v>4.62</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,28 +5111,28 @@
         <v>7.18</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="H68" t="n">
-        <v>5921.5</v>
+        <v>5787</v>
       </c>
       <c r="I68" t="n">
         <v>5830.778863532405</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K68" t="n">
-        <v>-2.96</v>
+        <v>-5.16</v>
       </c>
       <c r="L68" t="n">
-        <v>4.7</v>
+        <v>6.37</v>
       </c>
       <c r="M68" t="n">
         <v>2.27</v>
       </c>
       <c r="N68" t="n">
-        <v>2.19</v>
+        <v>2.27</v>
       </c>
       <c r="O68" t="n">
         <v>1.38</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>7.09</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="H69" t="n">
-        <v>5262</v>
+        <v>5374</v>
       </c>
       <c r="I69" t="n">
         <v>5352.809044950177</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K69" t="n">
-        <v>9.07</v>
+        <v>7.14</v>
       </c>
       <c r="L69" t="n">
         <v>2.37</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>5</v>
+      </c>
+      <c r="U69" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="70">
@@ -4410,22 +5249,22 @@
         <v>6.37</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="H70" t="n">
-        <v>5308.5</v>
+        <v>5250</v>
       </c>
       <c r="I70" t="n">
         <v>5295.999575538833</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K70" t="n">
-        <v>-1.22</v>
+        <v>-2.31</v>
       </c>
       <c r="L70" t="n">
-        <v>2.58</v>
+        <v>2.94</v>
       </c>
       <c r="M70" t="n">
         <v>1.95</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>3</v>
+      </c>
+      <c r="U70" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -4491,6 +5342,14 @@
       <c r="Q71" t="n">
         <v>40</v>
       </c>
+      <c r="R71" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9449,7 +10308,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>59.9</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="6">
@@ -9459,7 +10318,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7">
@@ -9469,7 +10328,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="8">
@@ -9479,7 +10338,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -9489,7 +10348,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10">
@@ -9499,7 +10358,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>108.2</v>
+        <v>110.2</v>
       </c>
     </row>
     <row r="11">
@@ -9509,7 +10368,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12">
@@ -9519,7 +10378,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13">
@@ -9529,7 +10388,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>29</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="14">
@@ -9539,7 +10398,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.55</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="15">
@@ -9549,7 +10408,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6.46</v>
+        <v>3.98</v>
       </c>
     </row>
     <row r="16">
@@ -9559,7 +10418,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5600000000000001</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="17">
@@ -9569,7 +10428,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>36.44</v>
+        <v>29.43</v>
       </c>
     </row>
     <row r="18">
@@ -9579,7 +10438,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>49.3</v>
+        <v>40.6</v>
       </c>
     </row>
     <row r="19">
@@ -9589,7 +10448,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.38</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="20">
@@ -9599,7 +10458,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.13</v>
+        <v>4.54</v>
       </c>
     </row>
     <row r="21">
@@ -9609,7 +10468,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10.65</v>
+        <v>14.73</v>
       </c>
     </row>
     <row r="22">
@@ -9619,7 +10478,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23">
@@ -9629,7 +10488,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -9639,7 +10498,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="25">
@@ -9659,7 +10518,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.82</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="27">
@@ -9679,7 +10538,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29">
